--- a/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/19062026.xlsx
+++ b/WhatsAppExcelMonitorElevenLabsV2/scripts/excel/19062026.xlsx
@@ -1,117 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Evangelio y Oraciones" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evangelio y Oraciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="24">
-  <si>
-    <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>APELLIDO_PATERNO</t>
-  </si>
-  <si>
-    <t>APELLIDO_MATERNO</t>
-  </si>
-  <si>
-    <t>CELULAR</t>
-  </si>
-  <si>
-    <t>MAIL</t>
-  </si>
-  <si>
-    <t>CORREO</t>
-  </si>
-  <si>
-    <t>SMS</t>
-  </si>
-  <si>
-    <t>WHATSAPP</t>
-  </si>
-  <si>
-    <t>TEXTO_MENSAJE</t>
-  </si>
-  <si>
-    <t>Alejandro</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>56994148421</t>
-  </si>
-  <si>
-    <t>lucesalejandro3@gmail.com</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">viernes, 19 de junio de 2026
-*Evangelio del Día*
-Lectura del santo evangelio según san Mateo
-Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
-*Oración de la mañana*
-Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
-Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
-Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
-Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
-  </si>
-  <si>
-    <t>Omar</t>
-  </si>
-  <si>
-    <t>56973223070</t>
-  </si>
-  <si>
-    <t>Mama</t>
-  </si>
-  <si>
-    <t>56971748545</t>
-  </si>
-  <si>
-    <t>Victor</t>
-  </si>
-  <si>
-    <t>56931123918</t>
-  </si>
-  <si>
-    <t>Yume</t>
-  </si>
-  <si>
-    <t>584146711206</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -135,28 +51,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,193 +456,491 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="8" width="5" customWidth="1"/>
-    <col min="9" max="9" width="100" style="1" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="8"/>
+    <col width="100" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>NOMBRES</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_PATERNO</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>APELLIDO_MATERNO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>CELULAR</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>MAIL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>CORREO</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>WHATSAPP</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TEXTO_MENSAJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>56994148421</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+    <row r="3" ht="150" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>56973223070</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mama</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>56971748545</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+    <row r="5" ht="150" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Victor</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56931123918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Yume</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>584146711206</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>lucesalejandro3@gmail.com</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>15</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="150" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mariangely</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>56972028078</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>mariangelygonzalez14@gmail.com</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>15</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MANUEL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LUCES</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>34672527995</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>alejandroluces5515@gmail.com</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Marianny</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Gonzalez</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>56967970252</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>marikaro2508@gmail.com</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Milagros</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>González</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>56936637515</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Milagrosghurtado@gmail.com</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>viernes, 19 de junio de 2026
+*Evangelio del Día*
+Lectura del santo evangelio según san Mateo
+Mateo 6, 19-23 En aquel tiempo, Jesús dijo a sus discípulos: “No acumulen ustedes tesoros en la tierra, donde la polilla y el moho los destruyen, donde los ladrones perforan las paredes y se los roban. Más bien acumulen tesoros en el cielo, donde ni la polilla ni el moho los destruyen, ni hay ladrones que perforen las paredes y se los roben; porque donde está tu tesoro, ahí también está tu corazón. Tus ojos son la luz de tu cuerpo; de manera que, si tus ojos están sanos, todo tu cuerpo tendrá luz. Pero si tus ojos están enfermos, todo tu cuerpo tendrá oscuridad. Y si lo que en ti debería ser luz, no es más que oscuridad, ¡qué negra no será tu propia oscuridad!”
+*Oración de la mañana*
+Señor Jesús, en tu sabiduría nos has enseñado a no acumular tesoros en la tierra, sino a buscar los tesoros del cielo. Ayúdame a entender que lo verdaderamente valioso no es lo material, sino el amor, la paz y la justicia. Que mi corazón se llene de estos tesoros celestiales y que mis ojos estén sanos para ver tu luz en todo y en todos.
+Padre amado, te doy gracias por este nuevo día, por la oportunidad de aprender y crecer, de buscar y encontrar los tesoros celestiales que nos ofreces. Ayúdame a recordar que donde está mi tesoro, ahí está mi corazón. Que mi corazón esté siempre contigo, en tu amor y en tu paz.
+Espíritu Santo, iluminador de almas, te pido que hagas brillar tu luz en mi vida. Si mis ojos están enfermos, cura mi ceguera para que pueda ver la belleza de tu creación, para que pueda reconocer la presencia de Dios en cada persona y en cada situación. Que mi corazón sea luz, no oscuridad, reflejando siempre el amor de Dios.
+Todo esto te lo pido en el nombre del Padre, del Hijo y del Espíritu Santo. Amén.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>